--- a/artfynd/A 48947-2021 artfynd.xlsx
+++ b/artfynd/A 48947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795050</v>
       </c>
       <c r="B2" t="n">
-        <v>101242</v>
+        <v>101243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48947-2021 artfynd.xlsx
+++ b/artfynd/A 48947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795050</v>
       </c>
       <c r="B2" t="n">
-        <v>101243</v>
+        <v>101249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48947-2021 artfynd.xlsx
+++ b/artfynd/A 48947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795050</v>
       </c>
       <c r="B2" t="n">
-        <v>101249</v>
+        <v>101252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48947-2021 artfynd.xlsx
+++ b/artfynd/A 48947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795050</v>
       </c>
       <c r="B2" t="n">
-        <v>101252</v>
+        <v>101257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48947-2021 artfynd.xlsx
+++ b/artfynd/A 48947-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131795050</v>
       </c>
       <c r="B2" t="n">
-        <v>101257</v>
+        <v>101260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48947-2021 artfynd.xlsx
+++ b/artfynd/A 48947-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131795050</v>
+        <v>167984</v>
       </c>
       <c r="B2" t="n">
-        <v>101304</v>
+        <v>83298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hökbäcklandet, Jmt</t>
+          <t>Hökbäckslandet ca 2,5 km NO om Midskog, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514160</v>
+        <v>514077</v>
       </c>
       <c r="R2" t="n">
-        <v>7013139</v>
+        <v>7013166</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-04-15</t>
+          <t>2002-05-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,19 +758,451 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>i gammal fuktig granskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>sparsam på döda rötter/kvistar vid basen av grov (40 cm dbh) gran</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>malin almquist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>132246015</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92546</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>760</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Midskogstjärnen, Midskogstjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>514061</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7013100</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134114831</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103762</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Midskogsberget, Midskogsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>513414</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7012819</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ella Hambeson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ella Hambeson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134114838</v>
+      </c>
+      <c r="B5" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Midskogsberget, Midskogsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>513419</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7012819</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Tallskog på blockmark</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ella Hambeson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ella Hambeson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131795050</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hökbäcklandet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>514160</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7013139</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-04-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Pontus Wallén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Pontus Wallén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>

--- a/artfynd/A 48947-2021 artfynd.xlsx
+++ b/artfynd/A 48947-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/167984</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132246015</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134114831</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134114838</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,8 +1232,20 @@
           <t>LstZ naturvärdesinventeringar mellan åren xxxx-xxxx</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131795050</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>